--- a/excelCfg/boss_affix.xlsx
+++ b/excelCfg/boss_affix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="affix" sheetId="1" r:id="R136d2cf6225445a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="affix" sheetId="1" r:id="R3b64410d10bf49a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -760,7 +760,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="46" t="str">
-        <x:v>移动速度提高，数值随 PVE 难度成长。</x:v>
+        <x:v>移动速度提高。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -786,7 +786,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="48" t="str">
-        <x:v>攻击基础值提高，数值随 PVE 难度成长。</x:v>
+        <x:v>攻击基础值提高；实际加值按目标变体的最终攻击值计算。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -812,7 +812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="48" t="str">
-        <x:v>攻击速度提高，数值随 PVE 难度成长。</x:v>
+        <x:v>攻击速度提高。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -838,7 +838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="48" t="str">
-        <x:v>护甲提高，数值随 PVE 难度成长。</x:v>
+        <x:v>护甲提高。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -864,7 +864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="48" t="str">
-        <x:v>最大生命提高，数值随 PVE 难度成长。</x:v>
+        <x:v>最大生命提高；实际加值按目标变体的最终生命值计算。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -890,7 +890,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="48" t="str">
-        <x:v>每秒生命恢复提高，数值随 PVE 难度成长。</x:v>
+        <x:v>每秒生命恢复提高。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -916,7 +916,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="48" t="str">
-        <x:v>攻击有概率造成 1 秒眩晕，触发概率随 PVE 难度成长。</x:v>
+        <x:v>攻击有概率造成 1 秒眩晕。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -942,7 +942,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="48" t="str">
-        <x:v>攻击附带冰霜减速，持续时间随 PVE 难度成长。</x:v>
+        <x:v>攻击附带冰霜减速，持续 2 秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -968,7 +968,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="51" t="str">
-        <x:v>攻击反馈法力并造成等额伤害，数值随 PVE 难度成长。</x:v>
+        <x:v>攻击反馈法力并造成等额伤害。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -977,7 +977,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a394e8781d4aca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6c334d1eb2b4208"/>
   </x:tableParts>
 </x:worksheet>
 </file>